--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487115_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487115_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>A. FRECHILLA GOMEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.521</v>
+        <v>1.807</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8503</v>
+        <v>1.5785</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3292</v>
+        <v>0.2285</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2702</v>
+        <v>1.2229</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1998</v>
+        <v>-0.3094</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9297</v>
+        <v>1.5323</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3036</v>
+        <v>1.2691</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2471</v>
+        <v>-0.1554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0564</v>
+        <v>1.4245</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0334</v>
+        <v>-0.0462</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0473</v>
+        <v>-0.154</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9861</v>
+        <v>0.1078</v>
       </c>
       <c r="P2" t="n">
-        <v>-5.0182</v>
+        <v>1.9301</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.9483</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6395</v>
+        <v>-0.118</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4094</v>
+        <v>0.3094</v>
       </c>
       <c r="U2" t="n">
-        <v>1.23</v>
+        <v>-0.4274</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3704</v>
+        <v>-1.228</v>
       </c>
       <c r="W2" t="n">
-        <v>2.0856</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4559</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FRECHILLA GOMEZ</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8754</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4595</v>
+        <v>1.9258</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4159</v>
+        <v>-1.2126</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2229</v>
+        <v>4.2702</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3094</v>
+        <v>5.1998</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5323</v>
+        <v>-0.9297</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2691</v>
+        <v>5.3036</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1554</v>
+        <v>5.2471</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4245</v>
+        <v>0.0564</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0462</v>
+        <v>-1.0334</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.154</v>
+        <v>-0.0473</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1078</v>
+        <v>-0.9861</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9301</v>
+        <v>-5.0182</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-6.9483</v>
       </c>
       <c r="R3" t="n">
         <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0496</v>
+        <v>1.8316</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1904</v>
+        <v>1.4849</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.24</v>
+        <v>0.3466</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.228</v>
+        <v>-0.3704</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.0856</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. AREVALO NEGUERUELA</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.369</v>
+        <v>-0.1255</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5128</v>
+        <v>-1.2652</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1438</v>
+        <v>1.1397</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1582</v>
+        <v>1.4125</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1924</v>
+        <v>2.7428</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0343</v>
+        <v>-1.3302</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08210000000000001</v>
+        <v>2.0588</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0414</v>
+        <v>2.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0407</v>
+        <v>-0.6112</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2403</v>
+        <v>-0.6463</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2338</v>
+        <v>0.0728</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0064</v>
+        <v>-0.719</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.386</v>
+        <v>-3.6672</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-5.9833</v>
       </c>
       <c r="R4" t="n">
-        <v>0.579</v>
+        <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1752</v>
+        <v>-0.2846</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3702</v>
+        <v>0.2456</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.195</v>
+        <v>-0.5302</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7991</v>
+        <v>-0.4383</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2111</v>
+        <v>-0.2518</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.588</v>
+        <v>-0.1865</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2862</v>
@@ -844,13 +844,13 @@
         <v>1.158</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0588</v>
+        <v>0.4197</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2657</v>
+        <v>0.2251</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2069</v>
+        <v>0.1946</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5717</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>A. AREVALO NEGUERUELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7406</v>
+        <v>-0.5961</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3449</v>
+        <v>-0.7131</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.117</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4125</v>
+        <v>-0.1582</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7428</v>
+        <v>-0.1924</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3302</v>
+        <v>0.0343</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0588</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>2.67</v>
+        <v>0.0414</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6112</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6463</v>
+        <v>-0.2403</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0728</v>
+        <v>-0.2338</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.719</v>
+        <v>-0.0064</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.6672</v>
+        <v>-0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.9833</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3161</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8997</v>
+        <v>-0.0519</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8341</v>
+        <v>0.1699</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0656</v>
+        <v>-0.2218</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4137</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4137</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1666</v>
+        <v>-2.4151</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.6189</v>
+        <v>-1.0635</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4523</v>
+        <v>-1.3516</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5114</v>
+        <v>-0.7083</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8516</v>
+        <v>0.0457</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3402</v>
+        <v>-0.754</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2684</v>
+        <v>-0.1553</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7908</v>
+        <v>-0.114</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0592</v>
+        <v>-0.0414</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7798</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0607</v>
+        <v>0.1597</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.719</v>
+        <v>-0.7126</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0532</v>
+        <v>-1.158</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1231</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7251</v>
+        <v>-0.2509</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8341</v>
+        <v>0.2499</v>
       </c>
       <c r="U7" t="n">
-        <v>0.109</v>
+        <v>-0.5007</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6891</v>
+        <v>-2.421</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0431</v>
+        <v>-3.7394</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.646</v>
+        <v>1.3185</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7083</v>
+        <v>-0.5114</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0457</v>
+        <v>-1.8516</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.754</v>
+        <v>1.3402</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1553</v>
+        <v>0.2684</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.114</v>
+        <v>-1.7908</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0414</v>
+        <v>2.0592</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.7798</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1597</v>
+        <v>-0.0607</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7126</v>
+        <v>-0.719</v>
       </c>
       <c r="P8" t="n">
-        <v>0.386</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.158</v>
+        <v>-4.0532</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5249</v>
+        <v>0.0205</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7297</v>
+        <v>0.0453</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7952</v>
+        <v>-0.0248</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.367999999999999</v>
+        <v>-3.4758</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.421</v>
+        <v>-3.5287</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05310000000000015</v>
+        <v>0.05300000000000016</v>
       </c>
       <c r="G9" t="n">
         <v>5.241499999999999</v>
@@ -1129,10 +1129,10 @@
         <v>-1.3673</v>
       </c>
       <c r="J9" t="n">
-        <v>9.507899999999999</v>
+        <v>9.507900000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>7.2799</v>
+        <v>7.279899999999999</v>
       </c>
       <c r="L9" t="n">
         <v>2.2278</v>
@@ -1147,7 +1147,7 @@
         <v>-3.5951</v>
       </c>
       <c r="P9" t="n">
-        <v>-8.685400000000001</v>
+        <v>-8.6854</v>
       </c>
       <c r="Q9" t="n">
         <v>-20.2658</v>
@@ -1156,10 +1156,10 @@
         <v>11.5805</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6742000000000001</v>
+        <v>1.5664</v>
       </c>
       <c r="T9" t="n">
-        <v>1.837800000000001</v>
+        <v>2.7301</v>
       </c>
       <c r="U9" t="n">
         <v>-1.1637</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>5.4292</v>
+        <v>5.5258</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0604</v>
+        <v>3.3279</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6312</v>
+        <v>2.1979</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6071</v>
+        <v>1.8003</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3105</v>
+        <v>3.0148</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2966</v>
+        <v>-1.2145</v>
       </c>
       <c r="J10" t="n">
-        <v>5.4486</v>
+        <v>2.7076</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0452</v>
+        <v>3.8965</v>
       </c>
       <c r="L10" t="n">
-        <v>4.4034</v>
+        <v>-1.1888</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8415</v>
+        <v>-0.9074</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7347</v>
+        <v>-0.8817</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1067</v>
+        <v>-0.0257</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.158</v>
+        <v>3.0881</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7371</v>
+        <v>3.0881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5242</v>
+        <v>-0.5906</v>
       </c>
       <c r="T10" t="n">
-        <v>1.051</v>
+        <v>-0.6077</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5268</v>
+        <v>0.0172</v>
       </c>
       <c r="V10" t="n">
-        <v>2.4559</v>
+        <v>1.228</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4559</v>
+        <v>1.228</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.8278</v>
+        <v>5.5164</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5234</v>
+        <v>5.5597</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3044</v>
+        <v>-0.0433</v>
       </c>
       <c r="G11" t="n">
-        <v>0.372</v>
+        <v>3.6071</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8569</v>
+        <v>0.3105</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4848</v>
+        <v>3.2966</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8409</v>
+        <v>5.4486</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9455</v>
+        <v>1.0452</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8954</v>
+        <v>4.4034</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4689</v>
+        <v>-1.8415</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0886</v>
+        <v>-0.7347</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3802</v>
+        <v>-1.1067</v>
       </c>
       <c r="P11" t="n">
+        <v>-1.158</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-2.8951</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.7371</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-0.965</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.7021</v>
-      </c>
       <c r="S11" t="n">
-        <v>1.1204</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3617</v>
+        <v>0.5503</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2413</v>
+        <v>0.0611</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5983</v>
+        <v>2.4559</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2859</v>
+        <v>2.4559</v>
       </c>
       <c r="X11" t="n">
-        <v>1.3125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6384</v>
+        <v>4.4074</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6269</v>
+        <v>2.6221</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0115</v>
+        <v>1.7853</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8003</v>
+        <v>0.372</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0148</v>
+        <v>0.8569</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2145</v>
+        <v>-0.4848</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7076</v>
+        <v>2.8409</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8965</v>
+        <v>1.9455</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1888</v>
+        <v>0.8954</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9074</v>
+        <v>-2.4689</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8817</v>
+        <v>-1.0886</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0257</v>
+        <v>-1.3802</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0881</v>
+        <v>1.7371</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>3.0881</v>
+        <v>2.7021</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.478</v>
+        <v>0.7</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3087</v>
+        <v>0.4604</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1692</v>
+        <v>0.2396</v>
       </c>
       <c r="V12" t="n">
-        <v>1.228</v>
+        <v>1.5983</v>
       </c>
       <c r="W12" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.3125</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7832</v>
+        <v>1.4974</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2782</v>
+        <v>0.7789</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5051</v>
+        <v>0.7186</v>
       </c>
       <c r="G13" t="n">
         <v>0.9091</v>
@@ -1468,13 +1468,13 @@
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1488</v>
+        <v>-0.4346</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8923</v>
+        <v>-0.3916</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2565</v>
+        <v>-0.043</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3281</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0376</v>
+        <v>-0.0431</v>
       </c>
       <c r="E14" t="n">
         <v>-2.1697</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2073</v>
+        <v>2.1266</v>
       </c>
       <c r="G14" t="n">
         <v>0.199</v>
@@ -1546,13 +1546,13 @@
         <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1547</v>
+        <v>0.074</v>
       </c>
       <c r="T14" t="n">
         <v>0.0727</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0819</v>
+        <v>0.0013</v>
       </c>
       <c r="V14" t="n">
         <v>1.228</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1676</v>
+        <v>-0.8551</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9385</v>
+        <v>-1.8398</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7709</v>
+        <v>0.9847</v>
       </c>
       <c r="G15" t="n">
         <v>-2.0496</v>
@@ -1624,13 +1624,13 @@
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.1064</v>
       </c>
       <c r="T15" t="n">
-        <v>1.051</v>
+        <v>0.1497</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2571</v>
+        <v>-0.0433</v>
       </c>
       <c r="V15" t="n">
         <v>-1.228</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5358</v>
+        <v>-1.0952</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1468</v>
+        <v>-0.9465</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.389</v>
+        <v>-0.1487</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4176</v>
@@ -1702,13 +1702,13 @@
         <v>2.7021</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3378</v>
+        <v>0.7783</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2862</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2518</v>
+        <v>0.4921</v>
       </c>
       <c r="V16" t="n">
         <v>-1.228</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9477</v>
+        <v>-1.3818</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6527</v>
+        <v>-1.3011</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7049</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.452</v>
+        <v>-2.3944</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4181</v>
+        <v>-1.9696</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0339</v>
+        <v>-0.4248</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2117</v>
+        <v>-1.4667</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0828</v>
+        <v>-0.9212</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2945</v>
+        <v>-0.5455</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2403</v>
+        <v>-0.9277</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5009</v>
+        <v>-1.0484</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2606</v>
+        <v>0.1207</v>
       </c>
       <c r="P17" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6888</v>
+        <v>0.4336</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4759</v>
+        <v>0.1656</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2128</v>
+        <v>0.268</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4255</v>
+        <v>-1.4672</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7471</v>
+        <v>-2.2521</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6784</v>
+        <v>0.7849</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3039</v>
+        <v>-1.452</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3446</v>
+        <v>-0.4181</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0407</v>
+        <v>-1.0339</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5441</v>
+        <v>-1.2117</v>
       </c>
       <c r="K18" t="n">
         <v>0.0828</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6269</v>
+        <v>-1.2945</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2402</v>
+        <v>-0.2403</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4274</v>
+        <v>-0.5009</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6676</v>
+        <v>0.2606</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.193</v>
+        <v>0.193</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7006</v>
+        <v>-0.2082</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.238</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4627</v>
+        <v>-0.1329</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4572</v>
+        <v>-1.9847</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0021</v>
+        <v>-1.5468</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4551</v>
+        <v>-0.4378</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3944</v>
+        <v>-0.3039</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9696</v>
+        <v>-0.3446</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4248</v>
+        <v>0.0407</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4667</v>
+        <v>-0.5441</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9212</v>
+        <v>0.0828</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5455</v>
+        <v>-0.6269</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9277</v>
+        <v>0.2402</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0484</v>
+        <v>-0.4274</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1207</v>
+        <v>0.6676</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>-0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6418</v>
+        <v>-0.2598</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5354</v>
+        <v>-0.0377</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1064</v>
+        <v>-0.2221</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8143</v>
+        <v>-3.0817</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.885</v>
+        <v>-2.2855</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9294</v>
+        <v>-0.7962</v>
       </c>
       <c r="G20" t="n">
         <v>-4.5115</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>1.053</v>
+        <v>0.7856</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9915</v>
+        <v>0.591</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0614</v>
+        <v>0.1946</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8999</v>
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4.3681</v>
+        <v>7.038200000000003</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.05299999999999927</v>
+        <v>-0.05289999999999839</v>
       </c>
       <c r="F21" t="n">
-        <v>4.421</v>
+        <v>7.0913</v>
       </c>
       <c r="G21" t="n">
         <v>-5.2415</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.6089</v>
+        <v>-6.608899999999999</v>
       </c>
       <c r="I21" t="n">
         <v>1.367500000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2663</v>
+        <v>4.266299999999998</v>
       </c>
       <c r="K21" t="n">
         <v>0.6711999999999998</v>
       </c>
       <c r="L21" t="n">
-        <v>3.595300000000001</v>
+        <v>3.5953</v>
       </c>
       <c r="M21" t="n">
         <v>-9.507899999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-7.28</v>
+        <v>-7.279999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.227700000000001</v>
+        <v>-2.2277</v>
       </c>
       <c r="P21" t="n">
         <v>8.6854</v>
@@ -2092,16 +2092,16 @@
         <v>20.2658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6739999999999999</v>
+        <v>1.9961</v>
       </c>
       <c r="T21" t="n">
         <v>1.1636</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8377</v>
+        <v>0.8326</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5982</v>
+        <v>1.598200000000001</v>
       </c>
       <c r="W21" t="n">
         <v>6.0977</v>
